--- a/results/Int Task Remove ACC -0.8/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.8/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.005872884982739624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03038029975283744</v>
+        <v>0.03037429861391547</v>
       </c>
       <c r="F3" t="n">
         <v>0.002184021847673482</v>
@@ -1166,28 +1166,28 @@
         <v>0.02170738218569015</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001512289489866254</v>
+        <v>-0.001518232208034216</v>
       </c>
       <c r="I3" t="n">
         <v>9.704229897145589e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04462877630977567</v>
+        <v>0.0446288581245064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02370123192096927</v>
+        <v>0.02369817568625045</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02369827246550908</v>
+        <v>0.02369532522118252</v>
       </c>
       <c r="M3" t="n">
         <v>0.01620193060290426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04006710725122923</v>
+        <v>0.04007008167121733</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02040442844032075</v>
+        <v>0.02040754856512574</v>
       </c>
       <c r="P3" t="n">
         <v>0.00727366524777433</v>
@@ -1196,7 +1196,7 @@
         <v>0.01600343528415791</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0155929201319423</v>
+        <v>0.01559591476216961</v>
       </c>
       <c r="S3" t="n">
         <v>0.2945550448381226</v>
@@ -1223,7 +1223,7 @@
         <v>0.002661589083606499</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03470825559115872</v>
+        <v>0.03471121504661891</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001387737771559038</v>
@@ -1298,13 +1298,13 @@
         <v>0.0005320627135546617</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01125657654009167</v>
+        <v>0.01125344272624021</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.00666491367052168</v>
+        <v>0.006668047484373138</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.006484855965215755</v>
+        <v>0.006481908720889201</v>
       </c>
       <c r="BC3" t="n">
         <v>-9.507847258011238e-06</v>
@@ -1319,7 +1319,7 @@
         <v>0.01421942358017777</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.004762547100275621</v>
+        <v>0.004756638680777837</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0003456636822469416</v>
@@ -1364,7 +1364,7 @@
         <v>0.04382902471669708</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.004557046064061585</v>
+        <v>0.004554097081460583</v>
       </c>
       <c r="BW3" t="n">
         <v>0.008279933859219038</v>
@@ -1385,7 +1385,7 @@
         <v>0.0008728987040084535</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002030676071023038</v>
+        <v>0.002033596139688045</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.0005948769398728627</v>
@@ -1406,7 +1406,7 @@
         <v>0.02972716091720777</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.008279933859219038</v>
+        <v>0.008282814873336005</v>
       </c>
       <c r="CK3" t="n">
         <v>0.007945659719451064</v>
@@ -1428,7 +1428,7 @@
         <v>0.01145012447400461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03270331462572621</v>
+        <v>0.0326977332214976</v>
       </c>
       <c r="F4" t="n">
         <v>0.002920908574377343</v>
@@ -1437,28 +1437,28 @@
         <v>0.05468928294964336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002939586377168131</v>
+        <v>0.002932396248453816</v>
       </c>
       <c r="I4" t="n">
         <v>0.001073030794171756</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04428233639547005</v>
+        <v>0.04427300376858116</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01291511426569985</v>
+        <v>0.0129175405019488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01292209968582649</v>
+        <v>0.01291972086388081</v>
       </c>
       <c r="M4" t="n">
         <v>0.03239192947161385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04062984032754178</v>
+        <v>0.04063808109722671</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02974371847460855</v>
+        <v>0.02975231977534511</v>
       </c>
       <c r="P4" t="n">
         <v>0.01821371798657882</v>
@@ -1467,7 +1467,7 @@
         <v>0.02031017484773797</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01792100922433967</v>
+        <v>0.01793626510389224</v>
       </c>
       <c r="S4" t="n">
         <v>0.1032683491624796</v>
@@ -1494,7 +1494,7 @@
         <v>0.01305070478122668</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03088476664660157</v>
+        <v>0.03088419839907405</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002761503144583464</v>
@@ -1569,13 +1569,13 @@
         <v>0.02021877752644144</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02812195219494185</v>
+        <v>0.02811479475603972</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008704581431167679</v>
+        <v>0.008711996682953943</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01477808628566346</v>
+        <v>0.0147795718627242</v>
       </c>
       <c r="BC4" t="n">
         <v>0.0006496816510989949</v>
@@ -1590,7 +1590,7 @@
         <v>0.02479461278151418</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.02423636988020874</v>
+        <v>0.02423991543767897</v>
       </c>
       <c r="BH4" t="n">
         <v>0.000935505780414492</v>
@@ -1635,7 +1635,7 @@
         <v>0.0447387708633238</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01937947570181254</v>
+        <v>0.01938458068038401</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0261320507024158</v>
@@ -1656,7 +1656,7 @@
         <v>0.002169735804199412</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01252959351135891</v>
+        <v>0.01251544511031948</v>
       </c>
       <c r="CD4" t="n">
         <v>0.004499814999036689</v>
@@ -1677,7 +1677,7 @@
         <v>0.03421238728413903</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0261320507024158</v>
+        <v>0.02613627851621273</v>
       </c>
       <c r="CK4" t="n">
         <v>0.007317152099463472</v>
@@ -1714,7 +1714,7 @@
         <v>-0.001444149720011745</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01063569682151593</v>
+        <v>-0.01060513447432767</v>
       </c>
       <c r="K5" t="n">
         <v>-0.003728913879846107</v>
@@ -1906,7 +1906,7 @@
         <v>-0.06554671382257585</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.02562665880271312</v>
+        <v>-0.02565614862872314</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.04966086700088472</v>
@@ -1927,7 +1927,7 @@
         <v>-0.001827291482463866</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.02452107279693483</v>
+        <v>-0.02446212791040373</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.007644259369423001</v>
@@ -2009,7 +2009,7 @@
         <v>0.005242907033318573</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002788123606643445</v>
+        <v>0.002765967033526753</v>
       </c>
       <c r="S6" t="n">
         <v>0.2532194299970584</v>
@@ -2036,7 +2036,7 @@
         <v>-0.005342995742301584</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01523069622563455</v>
+        <v>0.01523809486428504</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0004069974037743535</v>
@@ -2117,7 +2117,7 @@
         <v>0.0001794071762870275</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0009583889255230265</v>
+        <v>-0.0009657570363394124</v>
       </c>
       <c r="BC6" t="n">
         <v>-0.0004067618652026733</v>
@@ -2250,7 +2250,7 @@
         <v>0.00519781990208556</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0008550730223743586</v>
+        <v>-0.0008848172222553796</v>
       </c>
       <c r="I7" t="n">
         <v>-0.0001180899827373572</v>
@@ -2512,7 +2512,7 @@
         <v>0.009667835795490395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04049647216495166</v>
+        <v>0.04048926962965923</v>
       </c>
       <c r="F8" t="n">
         <v>0.00441173768307066</v>
@@ -2533,7 +2533,7 @@
         <v>0.03433030754257854</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03433030754257854</v>
+        <v>0.03432293943176216</v>
       </c>
       <c r="M8" t="n">
         <v>0.03964220691709713</v>
@@ -2740,7 +2740,7 @@
         <v>0.001442111896370884</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003074932137789066</v>
+        <v>0.0030526239878783</v>
       </c>
       <c r="CD8" t="n">
         <v>0.0003137230549890846</v>
@@ -2798,7 +2798,7 @@
         <v>0.001776198934280671</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1129089827483641</v>
+        <v>0.112879238548483</v>
       </c>
       <c r="K9" t="n">
         <v>0.03716395864106351</v>
@@ -2810,10 +2810,10 @@
         <v>0.0667256115531978</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1413741820345033</v>
+        <v>0.1414039262343843</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09419656786271453</v>
+        <v>0.09422776911076444</v>
       </c>
       <c r="P9" t="n">
         <v>0.04489859594383776</v>
@@ -2822,7 +2822,7 @@
         <v>0.06318891836133218</v>
       </c>
       <c r="R9" t="n">
-        <v>0.050029744199881</v>
+        <v>0.05008923259964305</v>
       </c>
       <c r="S9" t="n">
         <v>0.425609756097561</v>
@@ -2924,10 +2924,10 @@
         <v>0.02829833907865874</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06906925728611722</v>
+        <v>0.06903791914760264</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.02519586336571609</v>
+        <v>0.02522720150423065</v>
       </c>
       <c r="BB9" t="n">
         <v>0.03660294578502038</v>
@@ -3032,7 +3032,7 @@
         <v>0.0759369422962522</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.04278305963699228</v>
+        <v>0.04281186977816197</v>
       </c>
       <c r="CK9" t="n">
         <v>0.02061273051754904</v>
